--- a/data_analysis/PM_Worksheet.xlsx
+++ b/data_analysis/PM_Worksheet.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Link_Demo" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Viec_Can_Lam_Tiep" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Meeting_Notes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Test_Cases" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Tong_Quan'!$A$1:$E$12</definedName>
@@ -31,6 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'09_Link_Demo'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'10_Viec_Can_Lam_Tiep'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'11_Meeting_Notes'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'12_Test_Cases'!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -974,7 +976,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Viết demo checklist.</t>
+          <t>Chạy bộ test case demo trong QA_TEST_CASES.md.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -989,7 +991,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Chưa chạy</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -999,7 +1001,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Demo script, bug list, pass/fail checklist.</t>
+          <t>Test result pass/fail, bug list, action owner.</t>
         </is>
       </c>
     </row>
@@ -1093,6 +1095,670 @@
   <dataValidations count="1">
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chưa làm,Đang làm,Đang review,Bị chặn,Đã xong,Đang mở,Đã giảm rủi ro,Đang có,Thiếu,Chưa điền,Đã xong phần chính,Đã xong bản đầu"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mục tiêu</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Input/Endpoint</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Điều kiện</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Automated/Link</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>CHAT-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Chatbot</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Chào hỏi không gọi valuation</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>API/chatbot chạy được</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>intent=greeting, missing_fields=[], valuation=null, answer chào tự nhiên</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_greets_without_calling_valuation</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CHAT-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Chatbot</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Hỏi help/hướng dẫn</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>bạn có thể làm gì</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>API/chatbot chạy được</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>intent=help, answer nêu khả năng định giá/trend/snapshot</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_help_intent_direct</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CHAT-004</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Chatbot</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Hỏi trend</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>xu hướng thị trường Vinhomes Smart City căn hộ</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Có market data</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>intent=trend, có data.windows, answer có median hoặc caveat</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_trend_intent_direct</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CHAT-005</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Chatbot</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Hỏi snapshot/bảng giá</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>bảng giá tham khảo Vinhomes Smart City căn hộ</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Có snapshot data hoặc no_snapshot fallback</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>intent=snapshot, data có reference_price_snapshots</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_snapshot_intent_direct</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>MISS-001</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Missing info</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Thiếu project và diện tích</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>định giá căn 2PN</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Có retrieval data</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>missing_fields gồm project và area_m2, answer hỏi bổ sung</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_asks_for_missing_fields</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>MISS-002</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Missing info</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Thiếu diện tích nhưng có project</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>định giá căn hộ Vinhomes Smart City 2PN</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Có retrieval data</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>missing_fields=[area_m2], có gợi ý diện tích</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_suggests_nearest_info_when_area_missing</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SALE-001</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Valuation sale</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Định giá bán đủ dữ liệu</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Định giá bán căn hộ Vinhomes Smart City 54.2m2 2PN full nội thất</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Có listing data</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>intent=valuation, sample_size&gt;0, answer có P50/khoảng giá/độ tin cậy</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_valuation_from_vietnamese_text</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SALE-002</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Valuation sale</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm tra valuation đi qua LLM prompt</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>SALE-001</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>LLM enabled hoặc monkeypatch test</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>generate_answer valuation được gọi, context có example_answer</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>QA/Backend</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_valuation_routes_answer_through_llm_prompt</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>RENT-001</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Valuation rent</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Định giá thuê đủ dữ liệu</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Tôi có căn Vinhomes Smart City 54m², 2 phòng ngủ. Cho thuê được bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Có rent/listing data</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>intent=valuation, purpose=rent, answer có giá thuê/tháng</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>test_chat_rent_valuation_uses_structured_answer_format</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>LLM-001</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>LLM quality</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Câu trả lời tự nhiên, không máy móc</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SALE-001 chạy 3 lần</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Có OPENAI_API_KEY và MODEL</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Wording có thể khác nhau, số liệu vẫn đúng context</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>QA/Backend</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>QA_TEST_CASES.md</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Không so exact text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>API-001</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>API smoke</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Health check</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>GET /health</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Server chạy</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>HTTP 200, status=ok</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>test_health_endpoint</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>API-002</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>API smoke</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Projects list</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>GET /projects</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Config loaded</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>HTTP 200, có vinhomes-ocean-park</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Chưa chạy</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>test_projects_endpoint</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J13"/>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Chưa chạy,Pass,Fail,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2567,12 +3233,16 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Đã xong</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>QA_TEST_CASES.md</t>
+        </is>
+      </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Demo scenario</t>
@@ -2580,10 +3250,14 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Có script demo để test trước buổi trình bày.</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
+          <t>Có test case manual để QA/PM tick pass/fail trước demo.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Cần team chạy và cập nhật trạng thái từng case.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L9"/>
